--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486518_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486518_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0169</v>
+        <v>5.2607</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7294</v>
+        <v>6.1273</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7125</v>
+        <v>-0.8666</v>
       </c>
       <c r="G2" t="n">
         <v>2.6225</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7419</v>
+        <v>0.9857</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7677</v>
+        <v>1.1657</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0258</v>
+        <v>-0.18</v>
       </c>
       <c r="V2" t="n">
         <v>0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3792</v>
+        <v>4.2107</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6593</v>
+        <v>3.3984</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7199</v>
+        <v>0.8124</v>
       </c>
       <c r="G3" t="n">
         <v>2.355</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2808</v>
+        <v>0.5507</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0721</v>
+        <v>0.8112</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3529</v>
+        <v>-0.2605</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.756</v>
+        <v>3.5875</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0696</v>
+        <v>3.8086</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3136</v>
+        <v>-0.2211</v>
       </c>
       <c r="G4" t="n">
         <v>-3.2853</v>
@@ -766,13 +766,13 @@
         <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4762</v>
+        <v>1.3078</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1526</v>
+        <v>0.8917</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3236</v>
+        <v>0.4161</v>
       </c>
       <c r="V4" t="n">
         <v>3.3899</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.741</v>
+        <v>0.9405</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1462</v>
+        <v>2.4382</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4052</v>
+        <v>-1.4976</v>
       </c>
       <c r="G5" t="n">
         <v>2.0079</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4642</v>
+        <v>-0.2647</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2499</v>
+        <v>0.0421</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2143</v>
+        <v>-0.3067</v>
       </c>
       <c r="V5" t="n">
         <v>-1.8902</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3689</v>
+        <v>0.1454</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0667</v>
+        <v>-0.2903</v>
       </c>
       <c r="F6" t="n">
         <v>0.4356</v>
@@ -922,10 +922,10 @@
         <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6645</v>
+        <v>0.441</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4831</v>
+        <v>0.2596</v>
       </c>
       <c r="U6" t="n">
         <v>0.1815</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4612</v>
+        <v>0.0047</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2279</v>
+        <v>0.3183</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6891</v>
+        <v>-0.3136</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4835</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2468</v>
+        <v>-0.4107</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7634</v>
+        <v>-0.4829</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2292</v>
+        <v>0.2077</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2674</v>
+        <v>0.0547</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0382</v>
+        <v>0.153</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2543</v>
+        <v>-1.1013</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9794</v>
+        <v>-0.4654</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7251</v>
+        <v>-0.6359</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>0.006</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4146</v>
+        <v>0.1106</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4146</v>
+        <v>-0.1046</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. PREPELIC</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4705</v>
+        <v>-0.728</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0898</v>
+        <v>-0.0389</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6193</v>
+        <v>-0.6891</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.2903</v>
+        <v>-0.4835</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.2846</v>
+        <v>-1.2468</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0057</v>
+        <v>0.7634</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.6542</v>
+        <v>-0.2292</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.8342</v>
+        <v>-0.2674</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8199</v>
+        <v>0.0382</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6362</v>
+        <v>-0.2543</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4504</v>
+        <v>-0.9794</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1858</v>
+        <v>0.7251</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>5.4294</v>
+        <v>-0.2668</v>
       </c>
       <c r="T8" t="n">
-        <v>4.5665</v>
+        <v>0.1478</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8629</v>
+        <v>-0.4146</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3904</v>
+        <v>-0.1952</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>T. ROBERTS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4791</v>
+        <v>-1.6973</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0422</v>
+        <v>-1.5466</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4369</v>
+        <v>-0.1507</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-5.6891</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4107</v>
+        <v>-0.3893</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4829</v>
+        <v>-5.2998</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2077</v>
+        <v>-2.8394</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0547</v>
+        <v>0.8061</v>
       </c>
       <c r="L9" t="n">
-        <v>0.153</v>
+        <v>-3.6455</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1013</v>
+        <v>-2.8497</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4654</v>
+        <v>-1.1954</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6359</v>
+        <v>-1.6543</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0875</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>2.3926</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4778</v>
+        <v>1.1669</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2499</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2278</v>
+        <v>0.3064</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1952</v>
+        <v>2.8249</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.8249</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4412</v>
+        <v>-1.7531</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6307</v>
+        <v>-2.1585</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1896</v>
+        <v>0.4053</v>
       </c>
       <c r="G10" t="n">
         <v>-4.7009</v>
@@ -1234,13 +1234,13 @@
         <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7827</v>
+        <v>-0.0946</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3749</v>
+        <v>0.0973</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4077</v>
+        <v>-0.192</v>
       </c>
       <c r="V10" t="n">
         <v>2.8249</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6075</v>
+        <v>-2.3703</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1405</v>
+        <v>-2.78</v>
       </c>
       <c r="F11" t="n">
-        <v>0.533</v>
+        <v>0.4097</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2076</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4848</v>
+        <v>-0.2476</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3184</v>
+        <v>0.0421</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1663</v>
+        <v>-0.2896</v>
       </c>
       <c r="V11" t="n">
         <v>1.13</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. ROBERTS</t>
+          <t>B. PREPELIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,43 +1345,43 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4105</v>
+        <v>-3.1813</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1365</v>
+        <v>-3.5233</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.274</v>
+        <v>0.3419</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.6891</v>
+        <v>-6.2903</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3893</v>
+        <v>-3.2846</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.2998</v>
+        <v>-3.0057</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.8394</v>
+        <v>-3.6542</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8061</v>
+        <v>-2.8342</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.6455</v>
+        <v>-0.8199</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8497</v>
+        <v>-2.6362</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1954</v>
+        <v>-0.4504</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6543</v>
+        <v>-2.1858</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.3926</v>
@@ -1390,19 +1390,19 @@
         <v>2.3926</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5463</v>
+        <v>2.7185</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7294</v>
+        <v>2.133</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1831</v>
+        <v>0.5855</v>
       </c>
       <c r="V12" t="n">
-        <v>2.8249</v>
+        <v>0.3904</v>
       </c>
       <c r="W12" t="n">
-        <v>2.8249</v>
+        <v>0.3904</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.392</v>
+        <v>4.419499999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>4.726000000000001</v>
+        <v>5.753200000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3339</v>
+        <v>-1.333800000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-16.0128</v>
@@ -1438,7 +1438,7 @@
         <v>-6.1279</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.8849</v>
+        <v>-9.884900000000002</v>
       </c>
       <c r="J13" t="n">
         <v>-0.8155999999999999</v>
@@ -1453,7 +1453,7 @@
         <v>-15.1973</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.148899999999999</v>
+        <v>-7.1489</v>
       </c>
       <c r="O13" t="n">
         <v>-8.0486</v>
@@ -1468,13 +1468,13 @@
         <v>18.488</v>
       </c>
       <c r="S13" t="n">
-        <v>5.275399999999999</v>
+        <v>6.302900000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>5.534099999999999</v>
+        <v>6.5615</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2583</v>
+        <v>-0.2585000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>9.779199999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0474</v>
+        <v>2.1206</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1383</v>
+        <v>1.0265</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9091</v>
+        <v>1.094</v>
       </c>
       <c r="G14" t="n">
         <v>5.4873</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0702</v>
+        <v>0.003</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0721</v>
+        <v>-0.0396</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1423</v>
+        <v>0.0427</v>
       </c>
       <c r="V14" t="n">
         <v>-2.0647</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>O. MATULIONIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4798</v>
+        <v>1.6795</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0567</v>
+        <v>1.1458</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5768</v>
+        <v>0.5336</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8195</v>
+        <v>1.1105</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9428</v>
+        <v>1.7973</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8768</v>
+        <v>-0.6869</v>
       </c>
       <c r="J15" t="n">
-        <v>5.8078</v>
+        <v>2.404</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0616</v>
+        <v>2.2661</v>
       </c>
       <c r="L15" t="n">
-        <v>4.7461</v>
+        <v>0.1379</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9882</v>
+        <v>-1.2935</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1188</v>
+        <v>-0.4688</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8694</v>
+        <v>-0.8248</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.2626</v>
+        <v>1.5225</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.6552</v>
+        <v>-1.305</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3926</v>
+        <v>2.8276</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1181</v>
+        <v>-0.9535</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2091</v>
+        <v>0.0469</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.091</v>
+        <v>-1.0004</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1038</v>
+        <v>1.4503</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3814</v>
+        <v>1.9449</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2775</v>
+        <v>-0.4946</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6091</v>
+        <v>4.8195</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9764</v>
+        <v>0.9428</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6327</v>
+        <v>3.8768</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4022</v>
+        <v>5.8078</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5607</v>
+        <v>1.0616</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8415</v>
+        <v>4.7461</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7931</v>
+        <v>-0.9882</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5843</v>
+        <v>-0.1188</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2088</v>
+        <v>-0.8694</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>-3.2626</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>-5.6552</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3307</v>
+        <v>0.0886</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0036</v>
+        <v>0.0973</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3343</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1745</v>
+        <v>-0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1507</v>
+        <v>1.695</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3252</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. MATULIONIS</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6891</v>
+        <v>1.1724</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0341</v>
+        <v>2.064</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3449</v>
+        <v>-0.8915</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1105</v>
+        <v>3.551</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7973</v>
+        <v>0.2066</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6869</v>
+        <v>3.3444</v>
       </c>
       <c r="J17" t="n">
-        <v>2.404</v>
+        <v>1.9837</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2661</v>
+        <v>0.1095</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1379</v>
+        <v>1.8742</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2935</v>
+        <v>1.5673</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4688</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8248</v>
+        <v>1.4702</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8276</v>
+        <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9439</v>
+        <v>-0.5738</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0649</v>
+        <v>-0.1574</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.879</v>
+        <v>-0.4164</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3657</v>
+        <v>1.032</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6169</v>
+        <v>1.3814</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2512</v>
+        <v>-0.3494</v>
       </c>
       <c r="G18" t="n">
-        <v>3.551</v>
+        <v>1.6091</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2066</v>
+        <v>0.9764</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3444</v>
+        <v>0.6327</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9837</v>
+        <v>2.4022</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1095</v>
+        <v>1.5607</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8742</v>
+        <v>0.8415</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5673</v>
+        <v>-0.7931</v>
       </c>
       <c r="N18" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.5843</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4702</v>
+        <v>-0.2088</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2175</v>
+        <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3805</v>
+        <v>-0.4026</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6044</v>
+        <v>0.0036</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7761</v>
+        <v>-0.4062</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9347</v>
+        <v>-0.1745</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3252</v>
+        <v>1.1507</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2599</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0279</v>
+        <v>-0.4704</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8262</v>
+        <v>-0.6027</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2017</v>
+        <v>0.1323</v>
       </c>
       <c r="G19" t="n">
         <v>1.6401</v>
@@ -1936,13 +1936,13 @@
         <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9953</v>
+        <v>-1.4378</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5179</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2539</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3252</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3692</v>
+        <v>-0.529</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7699</v>
+        <v>-1.0994</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4007</v>
+        <v>0.5703</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3537</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>0.202</v>
+        <v>1.0422</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3305</v>
+        <v>0.3401</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5325</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6836</v>
+        <v>-2.1062</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.5217</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9442</v>
+        <v>-0.5846</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6568000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7982</v>
+        <v>0.3755</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0911</v>
+        <v>0.3088</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.293</v>
+        <v>0.0667</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2599</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. CAPALBO</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4613</v>
+        <v>-2.3484</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1317</v>
+        <v>-2.2029</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3296</v>
+        <v>-0.1456</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0476</v>
+        <v>-0.2417</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0516</v>
+        <v>0.4348</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.004</v>
+        <v>-0.6765</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2383</v>
+        <v>-2.0274</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2039</v>
+        <v>0.0547</v>
       </c>
       <c r="L22" t="n">
-        <v>1.0343</v>
+        <v>-2.0822</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1907</v>
+        <v>1.7857</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1523</v>
+        <v>0.3801</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0383</v>
+        <v>1.4056</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4213</v>
+        <v>-0.0643</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0227</v>
+        <v>-0.1754</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.444</v>
+        <v>0.1111</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.2599</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>L. CAPALBO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.536</v>
+        <v>-2.4125</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4264</v>
+        <v>-0.8022</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1097</v>
+        <v>-1.6103</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2417</v>
+        <v>0.0476</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4348</v>
+        <v>0.0516</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6765</v>
+        <v>-0.004</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0274</v>
+        <v>1.2383</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0547</v>
+        <v>0.2039</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0822</v>
+        <v>1.0343</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7857</v>
+        <v>-1.1907</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3801</v>
+        <v>-0.1523</v>
       </c>
       <c r="O23" t="n">
-        <v>1.4056</v>
+        <v>-1.0383</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2519</v>
+        <v>-0.3725</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.399</v>
+        <v>0.3521</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1471</v>
+        <v>-0.7246</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.2599</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.2599</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3922</v>
+        <v>-0.4116999999999993</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3338</v>
+        <v>1.3337</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.7258</v>
+        <v>-1.7458</v>
       </c>
       <c r="G24" t="n">
         <v>16.0129</v>
@@ -2305,7 +2305,7 @@
         <v>7.1489</v>
       </c>
       <c r="L24" t="n">
-        <v>8.048299999999999</v>
+        <v>8.048300000000001</v>
       </c>
       <c r="M24" t="n">
         <v>0.8154999999999997</v>
@@ -2326,19 +2326,19 @@
         <v>14.138</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.2755</v>
+        <v>-2.2952</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2583999999999997</v>
+        <v>0.2585000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.534</v>
+        <v>-2.5536</v>
       </c>
       <c r="V24" t="n">
         <v>-9.7791</v>
       </c>
       <c r="W24" t="n">
-        <v>4.3661</v>
+        <v>4.366099999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-14.1452</v>
